--- a/results/mummichog/PC_vs_Control/tables/mcg_pathwayanalysis_PC_vs_Control.xlsx
+++ b/results/mummichog/PC_vs_Control/tables/mcg_pathwayanalysis_PC_vs_Control.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="290">
   <si>
     <t>pathway</t>
   </si>
@@ -37,82 +37,628 @@
     <t>overlap_features (name)</t>
   </si>
   <si>
+    <t>Vitamin B1 (thiamin) metabolism</t>
+  </si>
+  <si>
+    <t>E282,E436,E579,E1403,E434,E281</t>
+  </si>
+  <si>
+    <t>C06157,C00020/C00362,C01081,C01136/C16255,C00020/C00362,C06157</t>
+  </si>
+  <si>
+    <t>[Dihydrolipoyllysine-residue succinyltransferase] S-glutaryldihydrolipoyllysine; S-Glutaryldihydrolipoamide-E$AMP/dGMP$Thiamin monophosphate; Thiamine monophosphate; Thiamin phosphate; Thiamine phosphate; TMP$S-Acetyldihydrolipoamide; 6-S-Acetyldihydrolipoamide/[Dihydrolipoyllysine-residue acetyltransferase] S-acetyldihydrolipoyllysine; S-Acetyldihydrolipoamide-E$AMP/dGMP$[Dihydrolipoyllysine-residue succinyltransferase] S-glutaryldihydrolipoyllysine; S-Glutaryldihydrolipoamide-E</t>
+  </si>
+  <si>
+    <t>Pyrimidine metabolism</t>
+  </si>
+  <si>
+    <t>E1188,E1305,E151,E1668,E436,E152,E1663,E434,E2768,E1190</t>
+  </si>
+  <si>
+    <t>C05711/C00475,C00214,C00526,C00399,C00020/C00362,C00526,C00399,C00020/C00362,C00299,C05711/C00475</t>
+  </si>
+  <si>
+    <t>gamma-Glutamyl-beta-cyanoalanine/Cytidine$Thymidine$Deoxyuridine$Ubiquinone$AMP/dGMP$Deoxyuridine$Ubiquinone$AMP/dGMP$Uridine$gamma-Glutamyl-beta-cyanoalanine/Cytidine</t>
+  </si>
+  <si>
+    <t>Omega-3 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>E436,E2151,E2832,E434</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C06426/C06427,C16300,C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$Stearidonic acid; 6,9,12,15-Octadecatetraenoic acid; (6Z,9Z,12Z,15Z)-Octadecatetraenoic acid$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Urea cycle/amino group metabolism</t>
+  </si>
+  <si>
+    <t>E1718,E452,E308,E2025,E2358,E201,E307,E25,E1015,E306,E2367,E408,E23,E1569,E454,E1129,E222,E24</t>
+  </si>
+  <si>
+    <t>C01449,C00170,C00547/C00314,C01250,C00624,CE2934,C00547/C00314,CE5536/C01586,C01137,C00547/C00314,C00750,C05589/C00788,CE5536/C01586,C00559/C05198,C00170,C00437,C00021,CE5536/C01586</t>
+  </si>
+  <si>
+    <t>Queuine; Base Q$5-Methylthioadenosine$Norepinephrine/Pyridoxine$N-Acetyl-L-glutamate 5-semialdehyde; 2-Acetamido-5-oxopentanoate$N-Acetyl-L-glutamate; N-Acetyl-L-glutamic acid$o-methylhippurate$Norepinephrine/Pyridoxine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$S-Adenosylmethioninamine$Norepinephrine/Pyridoxine$Spermine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$Deoxyadenosine/5'-Deoxyadenosine$5-Methylthioadenosine$N2-Acetyl-L-ornithine$S-Adenosyl-L-homocysteine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid</t>
+  </si>
+  <si>
+    <t>Lysine metabolism</t>
+  </si>
+  <si>
+    <t>E282,E2032,E436,E634,E434,E281,E222</t>
+  </si>
+  <si>
+    <t>C06157,C00579,C00020/C00362,C05545,C00020/C00362,C06157,C00021</t>
+  </si>
+  <si>
+    <t>[Dihydrolipoyllysine-residue succinyltransferase] S-glutaryldihydrolipoyllysine; S-Glutaryldihydrolipoamide-E$Dihydrolipoamide; Dihydrothioctamide$AMP/dGMP$Histone N6,N6-dimethyl-L-lysine$AMP/dGMP$[Dihydrolipoyllysine-residue succinyltransferase] S-glutaryldihydrolipoyllysine; S-Glutaryldihydrolipoamide-E$S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Alkaloid biosynthesis II</t>
+  </si>
+  <si>
+    <t>E269,E275,E436,E273,E434</t>
+  </si>
+  <si>
+    <t>C12448/egme,C12448/egme,C00020/C00362,C12448/egme,C00020/C00362</t>
+  </si>
+  <si>
+    <t>Ecgonine methyl ester; Methyl ecgonine/ecgonine methyl ester$Ecgonine methyl ester; Methyl ecgonine/ecgonine methyl ester$AMP/dGMP$Ecgonine methyl ester; Methyl ecgonine/ecgonine methyl ester$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Ubiquinone Biosynthesis</t>
+  </si>
+  <si>
+    <t>E1076,E2751,E1668,E436,E1077,E1663,E434,E222,E1081</t>
+  </si>
+  <si>
+    <t>C05838/C00811/C02763/C00166,C05350/C01197/C01179,C00399,C00020/C00362,C05838/C00811/C02763/C00166,C00399,C00020/C00362,C00021,C05838/C00811/C02763/C00166</t>
+  </si>
+  <si>
+    <t>cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate$Ubiquinone$AMP/dGMP$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$Ubiquinone$AMP/dGMP$S-Adenosyl-L-homocysteine$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate</t>
+  </si>
+  <si>
+    <t>Selenoamino acid metabolism</t>
+  </si>
+  <si>
+    <t>E436,E434,E624</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C00020/C00362,C00212/C00330</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$AMP/dGMP$Adenosine/Deoxyguanosine</t>
+  </si>
+  <si>
+    <t>Histidine metabolism</t>
+  </si>
+  <si>
+    <t>E1841,E436,E941,E79,E434,E222,E2653</t>
+  </si>
+  <si>
+    <t>C00439,C00020/C00362,C06486/C00386,CE2065,C00020/C00362,C00021,C03680</t>
+  </si>
+  <si>
+    <t>N-Formimidoyl-L-glutamate$AMP/dGMP$(6R)-6-(L-erythro-1,2-Dihydroxypropyl)-5,6,7,8-tetrahydro-4a-/Carnosine; Nalpha-(beta-alanyl)-L-histidine$acetylcarnosine$AMP/dGMP$S-Adenosyl-L-homocysteine$4-Imidazolone-5-propanoate</t>
+  </si>
+  <si>
+    <t>Tyrosine metabolism</t>
+  </si>
+  <si>
+    <t>E1283,E1084,E1088,E35,E1272,E408,E2737,E1085,E1500,E1089,E1117,E1086,E168,E1076,E294,E2751,E1173,E1087,E306,E1423,E1225,E1090,E1979,E1077,E23,E310,E307,E2260,E24,E308,E2525,E1092,E25,E668,E1982,E724,E1278,E312,E449,E1268,E434,E222,E2216,E313,E415,E1081,E2744,E1991,E436,E1281,E1435,E423</t>
+  </si>
+  <si>
+    <t>C09642,C05583/C05582,C00082/CE2174,C00355,C05588,C05589/C00788,C04043/C00642/C05852,C05583/C05582,tymsf,C00082/CE2174,C06350,C05583/C05582,CE5277,C05838/C00811/C02763/C00166,CE5276,C05350/C01197/C01179,C05581,C05583/C05582,C00547/C00314,C16586/CE2173,CE5542/C16353,C00082/CE2174,nrpphrsf,C05838/C00811/C02763/C00166,CE5536/C01586,C00822/C05604,C00547/C00314,C00588/C05594,CE5536/C01586,C00547/C00314,C15522/thbpt4acam,C00082/CE2174,CE5536/C01586,CE4888/C05578,nrpphrsf,C13690,C09642,C00822/C05604,C05606,C05588,C00020/C00362,C00021,C06199,C00822/C05604,C00079/CE2172,C05838/C00811/C02763/C00166,C05576,C05587/C07453,C00020/C00362,C09642,CE1918/CE5629,CE2176</t>
+  </si>
+  <si>
+    <t>(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$L-Tyrosine/$3,4-Dihydroxy-L-phenylalanine$L-Metanephrine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3,4-Dihydroxyphenylacetaldehyde; Protocatechuatealdehyde/4-Hydroxyphenylacetate/2-Hydroxyphenylacetate$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$Tyramine O-sulfate$L-Tyrosine/$$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$aminochrome o-semiquinone$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$dopamine o-quinone$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate/Caffeate; Caffeic acid; 3,4-Dihydroxy-trans-cinnamate; trans-Caffeate/3-(4-Hydroxyphenyl)pyruvate$3-Methoxy-4-hydroxyphenylacetaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$Norepinephrine/Pyridoxine$2-Phenyl-1,3-propanediol monocarbamate/$noradrenochrome o-semiquinone/$L-Tyrosine/$Sulfate derivative of norepinephrine$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Norepinephrine/Pyridoxine$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$Norepinephrine/Pyridoxine$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine/$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$dopaminochrome/5,6-Dihydroxyindole; DHI$Sulfate derivative of norepinephrine$Dopamine 3-O-sulfate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Melanin$L-Metanephrine$AMP/dGMP$S-Adenosyl-L-homocysteine$Hordenine; 4-[2-(Dimethylamino)ethyl]phenol$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Phenylalanine/$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$3,4-Dihydroxyphenylethyleneglycol$3-Methoxytyramine/Epinine; Deoxyepinephrine$AMP/dGMP$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-hydroxytryptophol/1,2-dehydrosalsolinol$3-O-methyldopa</t>
+  </si>
+  <si>
+    <t>Mono-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>E436,E434</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Phytanic acid peroxisomal oxidation</t>
+  </si>
+  <si>
+    <t>Vitamin A (retinol) metabolism</t>
+  </si>
+  <si>
+    <t>E54,E999,E1002,E908,E436,E434,E600,E907</t>
+  </si>
+  <si>
+    <t>CE5932/C02075/C06428/CE5013,C16679/C16677/C16680,C16679/C16677/C16680,C00777/C15493,C00020/C00362,C00020/C00362,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,C00777/C15493</t>
+  </si>
+  <si>
+    <t>13,14-epoxy-retinol/Retinyl ester; all-trans-Retinyl ester/(5Z,8Z,11Z,14Z,17Z)-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoic acid; Eicosapentaenoic acid; 5,8,11,14,17-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoate/$all-trans-18-Hydroxyretinoic acid/all-trans-4-Hydroxyretinoic acid/all-trans-5,6-Epoxyretinoic acid; all-trans-5,6-Epoxy-5,6-dihydroretinoic acid$all-trans-18-Hydroxyretinoic acid/all-trans-4-Hydroxyretinoic acid/all-trans-5,6-Epoxyretinoic acid; all-trans-5,6-Epoxy-5,6-dihydroretinoic acid$Retinoate/9-cis-Retinoic acid$AMP/dGMP$AMP/dGMP$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$Retinoate/9-cis-Retinoic acid</t>
+  </si>
+  <si>
+    <t>Methionine and cysteine metabolism</t>
+  </si>
+  <si>
+    <t>E2648,E452,E1015,E436,E454,E434,E624,E222</t>
+  </si>
+  <si>
+    <t>C02291/C00542,C00170,C01137,C00020/C00362,C00170,C00020/C00362,C00212/C00330,C00021</t>
+  </si>
+  <si>
+    <t>L-Cystathionine/Cystathionine$5-Methylthioadenosine$S-Adenosylmethioninamine$AMP/dGMP$5-Methylthioadenosine$AMP/dGMP$Adenosine/Deoxyguanosine$S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Vitamin B2 (riboflavin) metabolism</t>
+  </si>
+  <si>
+    <t>E436,E434,E2342,E2339</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C00020/C00362,C01847,C00061</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$AMP/dGMP$Reduced FMN; FMNH2$FMN</t>
+  </si>
+  <si>
+    <t>Biopterin metabolism</t>
+  </si>
+  <si>
+    <t>E2525,E1092,E1310,E1088,E1090,E1312,E1089,E415</t>
+  </si>
+  <si>
+    <t>C15522/thbpt4acam,C00082/CE2174,CE2705/CE5236,C00082/CE2174,C00082/CE2174,CE2705/CE5236,C00082/CE2174,C00079/CE2172</t>
+  </si>
+  <si>
+    <t>Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$L-Tyrosine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$L-Tyrosine/$L-Tyrosine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$L-Tyrosine/$L-Phenylalanine/</t>
+  </si>
+  <si>
+    <t>Vitamin B6 (pyridoxine) metabolism</t>
+  </si>
+  <si>
+    <t>E308,E306,E2085,E672,E307,E316</t>
+  </si>
+  <si>
+    <t>C00547/C00314,C00547/C00314,,,C00547/C00314,</t>
+  </si>
+  <si>
+    <t>Norepinephrine/Pyridoxine$Norepinephrine/Pyridoxine$$$Norepinephrine/Pyridoxine$</t>
+  </si>
+  <si>
+    <t>Electron transport chain</t>
+  </si>
+  <si>
+    <t>E1668,E1663</t>
+  </si>
+  <si>
+    <t>C00399,C00399</t>
+  </si>
+  <si>
+    <t>Ubiquinone$Ubiquinone</t>
+  </si>
+  <si>
+    <t>Fatty acid oxidation</t>
+  </si>
+  <si>
+    <t>Omega-6 fatty acid metabolism</t>
+  </si>
+  <si>
+    <t>De novo fatty acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E436,E54,E434,E2151</t>
+  </si>
+  <si>
+    <t>C00020/C00362,CE5932/C02075/C06428/CE5013,C00020/C00362,C06426/C06427</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$13,14-epoxy-retinol/Retinyl ester; all-trans-Retinyl ester/(5Z,8Z,11Z,14Z,17Z)-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoic acid; Eicosapentaenoic acid; 5,8,11,14,17-Icosapentaenoic acid; (5Z,8Z,11Z,14Z,17Z)-Eicosapentaenoate/$AMP/dGMP$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate</t>
+  </si>
+  <si>
     <t>Tryptophan metabolism</t>
   </si>
   <si>
-    <t>E33,E555,E412,E22,E32,E34,E359,E659,E413,E2090,E1465,E866,E228,E661,E214,E1568,E1048,E1472,E868,E415,E2124,E1049,E869,E1169,E870,E1260,E1263,E664,E370,E1192,E1283,E552,E1208,E1476,E666,E1275,E42,E1850,E452,E238,E1450,E54,E862,E209,E2300,E821,E357</t>
-  </si>
-  <si>
-    <t>C05639,C01598,C05645,C00780,C05639,C05639,CE2119/C05643,C06212,C05645,CE5538/C05653,C00637,CE3087,C00328/C05647,C06212,C05635/C16596,C00954/C05634,CE3140,C05660,C00078/C00525,C05645,CE2153,CE3140,C00078/C00525,CE2122,C00078/C00525,C02693,C02693,CE5860,C02406/C02700,C03227/C05651,CE6205,C01598,C05638,C05660,CE5860,CE6205,C01717,C02220,C00020/C00362,C00021,CE1918/CE5629,C01252,CE3087,C05635/C16596,C00398,C00643,CE2119/C05643</t>
-  </si>
-  <si>
-    <t>4,6-Dihydroxyquinoline; Quinoline-4,6-diol$Melatonin; N-Acetyl-5-methoxytryptamine$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$Serotonin$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$4,6-Dihydroxyquinoline; Quinoline-4,6-diol$/6-Hydroxymelatonin$N-Methylserotonin$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$noradrenochrome/N-Formylanthranilate$Indole-3-acetaldehyde$beta-carboline$L-Kynurenine/Formyl-5-hydroxykynurenamine$N-Methylserotonin$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$Indole-3-acetate/5-Hydroxyindoleacetaldehyde$$5-Methoxyindoleacetate$L-Tryptophan/D-Tryptophan$4-(2-Amino-3-hydroxyphenyl)-2,4-dioxobutanoate$$$L-Tryptophan/D-Tryptophan$methyl indole-3-acetate$L-Tryptophan/D-Tryptophan$Indole-3-acetamide$Indole-3-acetamide$$Formylkynurenine/L-Formylkynurenine$3-Hydroxy-L-kynurenine/5-Hydroxykynurenine; 5-Hydroxy-L-kynurenine$5-methoxytryptophol$Melatonin; N-Acetyl-5-methoxytryptamine$5-Hydroxykynurenamine$5-Methoxyindoleacetate$$5-methoxytryptophol$4-Hydroxy-2-quinolinecarboxylic acid$2-Aminomuconate$AMP/dGMP$S-Adenosyl-L-homocysteine$5-hydroxytryptophol/1,2-dehydrosalsolinol$4-(2-Aminophenyl)-2,4-dioxobutanoate$beta-carboline$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$Tryptamine$5-Hydroxy-L-tryptophan$/6-Hydroxymelatonin</t>
-  </si>
-  <si>
-    <t>Urea cycle/amino group metabolism</t>
-  </si>
-  <si>
-    <t>E318,E470,E1756,E1516,E36,E424,E38,E1733,E1008,E39,E217,E1146,E40,E467,E238,E1523,E1032,E420,E468</t>
-  </si>
-  <si>
-    <t>C00547/C00314,C00170,C02442/C03711,C04692,CE5536/C01586,C05589/C00788,CE5536/C01586,C01449,C03406,CE5536/C01586,CE2934,C00437,CE5536/C01586,C00170,C00021,C04692,C01137,C05589/C00788,C00170</t>
-  </si>
-  <si>
-    <t>Norepinephrine/Pyridoxine$5-Methylthioadenosine$N-Methyltyramine/N-Methylphenylethanolamine$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$Queuine; Base Q$N-(L-Arginino)succinate; 2-(Nomega-L-Arginino)succinate; L-Argininosuccinate; L-Argininosuccinic acid; L-Arginosuccinic acid$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$o-methylhippurate$N2-Acetyl-L-ornithine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$5-Methylthioadenosine$S-Adenosyl-L-homocysteine$Peptide 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; 2-[3-Carboxy-3-(methylammonio)propyl]-L-histidine; EF-2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine; Elongation factor 2 2-[3-carboxy-3-(methylammonio)propyl]-L-histidine$S-Adenosylmethioninamine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Methylthioadenosine</t>
-  </si>
-  <si>
-    <t>Alkaloid biosynthesis II</t>
-  </si>
-  <si>
-    <t>E289,E452,E290,E285,E291</t>
-  </si>
-  <si>
-    <t>C12448/egme,C00020/C00362,C12448/egme,C12448/egme,C12448/egme</t>
-  </si>
-  <si>
-    <t>Ecgonine methyl ester; Methyl ecgonine/ecgonine methyl ester$AMP/dGMP$Ecgonine methyl ester; Methyl ecgonine/ecgonine methyl ester$Ecgonine methyl ester; Methyl ecgonine/ecgonine methyl ester$Ecgonine methyl ester; Methyl ecgonine/ecgonine methyl ester</t>
-  </si>
-  <si>
-    <t>Biopterin metabolism</t>
-  </si>
-  <si>
-    <t>E1106,E903,E1109,E1327,E2207,E431,E1105,E1107,E426,E1325</t>
-  </si>
-  <si>
-    <t>C00082/CE2174,C04874,C00082/CE2174,CE2705/CE5236,C03684/C00835,C00079/CE2172,C00082/CE2174,C00082/CE2174,C00079/CE2172,CE2705/CE5236</t>
-  </si>
-  <si>
-    <t>L-Tyrosine/$Dihydroneopterin$L-Tyrosine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin$6-Pyruvoyl-5,6,7,8-tetrahydropterin/Sepiapterin$L-Phenylalanine/$L-Tyrosine/$L-Tyrosine/$L-Phenylalanine/$quinonoid dihydrobiopterin/O2'-4a-cyclic-tetrahydrobiopterin</t>
+    <t>E343,E539,E1550,E212,E643,E198,E399,E1450,E1456,E851,E38,E1033,E810,E1457,E1152,E852,E1243,E1266,E354,E2525,E1191,E648,E26,E9,E434,E222,E855,E1461,E193,E805,E1258,E436,E342,E1435,E846,E396,E18</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,,,,,,C15522/thbpt4acam,,,,,C00020/C00362,C00021,,,,,,C00020/C00362,,CE1918/CE5629,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$$$$$$Tetrahydrobiopterin-4a-carbinolamine/Tetrahydrobiopterin-4a-carbinolamine$$$$$AMP/dGMP$S-Adenosyl-L-homocysteine$$$$$$AMP/dGMP$$5-hydroxytryptophol/1,2-dehydrosalsolinol$$$</t>
+  </si>
+  <si>
+    <t>Pentose phosphate pathway</t>
+  </si>
+  <si>
+    <t>E171,E1185,E436,E434,E173</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
+  </si>
+  <si>
+    <t>E436,E517,E222,E434</t>
+  </si>
+  <si>
+    <t>C00020/C00362,,C00021,C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$$S-Adenosyl-L-homocysteine$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Vitamin E metabolism</t>
+  </si>
+  <si>
+    <t>E436,E959,E434</t>
+  </si>
+  <si>
+    <t>C00020/C00362,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>CoA Catabolism</t>
+  </si>
+  <si>
+    <t>E436,E434,E544</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C00020/C00362,</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$AMP/dGMP$</t>
+  </si>
+  <si>
+    <t>Fatty acid activation</t>
+  </si>
+  <si>
+    <t>E436,E2151,E434</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C06426/C06427,C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Glyoxylate and Dicarboxylate Metabolism</t>
+  </si>
+  <si>
+    <t>E173</t>
+  </si>
+  <si>
+    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
+  </si>
+  <si>
+    <t>E222</t>
+  </si>
+  <si>
+    <t>C00021</t>
+  </si>
+  <si>
+    <t>S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Porphyrin metabolism</t>
+  </si>
+  <si>
+    <t>E1596,E2894,E362,E2180,E136</t>
+  </si>
+  <si>
+    <t>,,,,</t>
+  </si>
+  <si>
+    <t>$$$$</t>
+  </si>
+  <si>
+    <t>Di-unsaturated fatty acid beta-oxidation</t>
+  </si>
+  <si>
+    <t>Valine, leucine and isoleucine degradation</t>
+  </si>
+  <si>
+    <t>Pentose and Glucuronate Interconversions</t>
+  </si>
+  <si>
+    <t>E173,E171</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Glycolysis and Gluconeogenesis</t>
+  </si>
+  <si>
+    <t>E436,E434,E2032,E1403</t>
+  </si>
+  <si>
+    <t>C00020/C00362,C00020/C00362,C00579,C01136/C16255</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$AMP/dGMP$Dihydrolipoamide; Dihydrothioctamide$S-Acetyldihydrolipoamide; 6-S-Acetyldihydrolipoamide/[Dihydrolipoyllysine-residue acetyltransferase] S-acetyldihydrolipoyllysine; S-Acetyldihydrolipoamide-E</t>
+  </si>
+  <si>
+    <t>Butanoate metabolism</t>
+  </si>
+  <si>
+    <t>E436,E2164,E295,E434</t>
+  </si>
+  <si>
+    <t>C00020/C00362,,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>AMP/dGMP$$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Drug metabolism - cytochrome P450</t>
+  </si>
+  <si>
+    <t>E420,E193,E208,E210,E416,E127,E1423,E211,E358,E812,E198,E207</t>
+  </si>
+  <si>
+    <t>,,,,,,C16586/CE2173,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$2-Phenyl-1,3-propanediol monocarbamate/$$$$$</t>
+  </si>
+  <si>
+    <t>Aspartate and asparagine metabolism</t>
+  </si>
+  <si>
+    <t>E2360,E434,E436,E2367,E1129,E1575</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,C00020/C00362,C00750,C00437,</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$AMP/dGMP$Spermine$N2-Acetyl-L-ornithine$</t>
+  </si>
+  <si>
+    <t>Bile acid biosynthesis</t>
+  </si>
+  <si>
+    <t>E759,E2515,E436,E1626,E434,E1627,E2265</t>
+  </si>
+  <si>
+    <t>,,C00020/C00362,,C00020/C00362,,</t>
+  </si>
+  <si>
+    <t>$$AMP/dGMP$$AMP/dGMP$$</t>
+  </si>
+  <si>
+    <t>Glycine, serine, alanine and threonine metabolism</t>
+  </si>
+  <si>
+    <t>E2722,E1238,E2032,E436,E798,E434,E222</t>
+  </si>
+  <si>
+    <t>,,C00579,C00020/C00362,,C00020/C00362,C00021</t>
+  </si>
+  <si>
+    <t>$$Dihydrolipoamide; Dihydrothioctamide$AMP/dGMP$$AMP/dGMP$S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Propanoate metabolism</t>
+  </si>
+  <si>
+    <t>Vitamin H (biotin) metabolism</t>
+  </si>
+  <si>
+    <t>Chondroitin sulfate degradation</t>
+  </si>
+  <si>
+    <t>Hexose phosphorylation</t>
+  </si>
+  <si>
+    <t>E987,E60,E1076,E1077,E986,E1081</t>
+  </si>
+  <si>
+    <t>,,C05838/C00811/C02763/C00166,C05838/C00811/C02763/C00166,,C05838/C00811/C02763/C00166</t>
+  </si>
+  <si>
+    <t>$$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate</t>
+  </si>
+  <si>
+    <t>Lipoate metabolism</t>
+  </si>
+  <si>
+    <t>E1640,E2032</t>
+  </si>
+  <si>
+    <t>,C00579</t>
+  </si>
+  <si>
+    <t>$Dihydrolipoamide; Dihydrothioctamide</t>
+  </si>
+  <si>
+    <t>Drug metabolism - other enzymes</t>
+  </si>
+  <si>
+    <t>E1378,E1496</t>
+  </si>
+  <si>
+    <t>Androgen and estrogen biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E1884,E348,E1349,E1164,E979,E709,E768,E980,E1165,E1876,E903,E748,E769,E222</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,C00021</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$S-Adenosyl-L-homocysteine</t>
+  </si>
+  <si>
+    <t>Arachidonic acid metabolism</t>
+  </si>
+  <si>
+    <t>E1008,E2387,E1060,E434,E436,E2151,E600</t>
+  </si>
+  <si>
+    <t>,,,C00020/C00362,C00020/C00362,C06426/C06427,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016</t>
+  </si>
+  <si>
+    <t>$$$AMP/dGMP$AMP/dGMP$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol</t>
+  </si>
+  <si>
+    <t>C21-steroid hormone biosynthesis and metabolism</t>
+  </si>
+  <si>
+    <t>E575,E1884,E979,E1349,E1164,E709,E768,E980,E903,E1876,E1165,E2139,E748,E769,E2493,E334</t>
+  </si>
+  <si>
+    <t>,,,,,,,,,,,,,,,</t>
+  </si>
+  <si>
+    <t>$$$$$$$$$$$$$$$</t>
+  </si>
+  <si>
+    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
+  </si>
+  <si>
+    <t>TCA cycle</t>
+  </si>
+  <si>
+    <t>E1668,E1663,E2032</t>
+  </si>
+  <si>
+    <t>C00399,C00399,C00579</t>
+  </si>
+  <si>
+    <t>Ubiquinone$Ubiquinone$Dihydrolipoamide; Dihydrothioctamide</t>
   </si>
   <si>
     <t>Arginine and Proline Metabolism</t>
   </si>
   <si>
-    <t>E1008,E467,E468,E1032,E470,E1855</t>
-  </si>
-  <si>
-    <t>C03406,C00170,C00170,C01137,C00170,C00147</t>
-  </si>
-  <si>
-    <t>N-(L-Arginino)succinate; 2-(Nomega-L-Arginino)succinate; L-Argininosuccinate; L-Argininosuccinic acid; L-Arginosuccinic acid$5-Methylthioadenosine$5-Methylthioadenosine$S-Adenosylmethioninamine$5-Methylthioadenosine$Adenine</t>
-  </si>
-  <si>
-    <t>Tyrosine metabolism</t>
-  </si>
-  <si>
-    <t>E1747,E1298,E318,E1515,E2090,E1105,E2215,E1090,E1289,E1756,E1101,E1993,E1799,E1106,E424,E36,E443,E1438,E1134,E1103,E184,E1801,E1107,E426,E1093,E49,E310,E38,E1104,E1242,E1190,E326,E39,E684,E2004,E740,E1109,E2268,E327,E2245,E40,E51,E465,E1295,E328,E1792,E1285,E452,E238,E420,E439,E329,E1450,E431,E1098,E2224,E1099</t>
-  </si>
-  <si>
-    <t>CE5627,C09642,C00547/C00314,tymsf,CE5538/C05653,C00082/CE2174,CE4890/C09640,C05838/C00811/C02763/C00166,C05588,C02442/C03711,C05583/C05582,nrpphrsf,C05580,C00082/CE2174,C05589/C00788,CE5536/C01586,CE2176,C16586/CE2173,C06350,C05583/C05582,CE5277,C05580,C00082/CE2174,C00079/CE2172,C05838/C00811/C02763/C00166,C00355,CE5276,CE5536/C01586,C05583/C05582,CE5542/C16353,C05581,C00822/C05604,CE5536/C01586,CE4888/C05578,C05587/C07453,C13690,C00082/CE2174,C00588/C05594,C00822/C05604,CE5025,CE5536/C01586,C00355,C05606,C09642,C00822/C05604,C02670/C00072/glac,C05588,C00020/C00362,C00021,C05589/C00788,CE2176,C00822/C05604,CE1918/CE5629,C00079/CE2172,C05838/C00811/C02763/C00166,C06199,C05583/C05582</t>
-  </si>
-  <si>
-    <t>salsoline-1-carboxylate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Norepinephrine/Pyridoxine$Tyramine O-sulfate$noradrenochrome/N-Formylanthranilate$L-Tyrosine/$N-methylsalsolinol/(-)-Salsoline$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$L-Metanephrine$N-Methyltyramine/N-Methylphenylethanolamine$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$Sulfate derivative of norepinephrine$3,4-Dihydroxymandelate$L-Tyrosine/$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate/$$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$aminochrome o-semiquinone$3,4-Dihydroxymandelate$L-Tyrosine/$L-Phenylalanine/$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$3,4-Dihydroxy-L-phenylalanine$dopamine o-quinone$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid$noradrenochrome o-semiquinone/$3-Methoxy-4-hydroxyphenylacetaldehyde$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$dopaminochrome/5,6-Dihydroxyindole; DHI$3-Methoxytyramine/Epinine; Deoxyepinephrine$Dopamine 3-O-sulfate$L-Tyrosine/$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$5-S-glutathionyl-dopamine$adrenochrome/Hippurate; Hippuric acid; N-Benzoylglycine; Benzoylaminoacetic acid$3,4-Dihydroxy-L-phenylalanine$Melanin$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$L-Metanephrine$AMP/dGMP$S-Adenosyl-L-homocysteine$L-Normetanephrine/L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-O-methyldopa$Dopaquinone/2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$5-hydroxytryptophol/1,2-dehydrosalsolinol$L-Phenylalanine/$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$Hordenine; 4-[2-(Dimethylamino)ethyl]phenol$3-Methoxy-4-hydroxyphenylglycolaldehyde/Homovanillate; Homovanillic acid</t>
-  </si>
-  <si>
-    <t>Drug metabolism - other enzymes</t>
-  </si>
-  <si>
-    <t>E1511,E1393,E1626</t>
+    <t>E1015,E454,E452</t>
+  </si>
+  <si>
+    <t>C01137,C00170,C00170</t>
+  </si>
+  <si>
+    <t>S-Adenosylmethioninamine$5-Methylthioadenosine$5-Methylthioadenosine</t>
+  </si>
+  <si>
+    <t>Vitamin D3 (cholecalciferol) metabolism</t>
+  </si>
+  <si>
+    <t>E4,E2515</t>
+  </si>
+  <si>
+    <t>Hyaluronan Metabolism</t>
+  </si>
+  <si>
+    <t>E552,E677</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
+  </si>
+  <si>
+    <t>E323,E324</t>
+  </si>
+  <si>
+    <t>Heparan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E677,E173</t>
+  </si>
+  <si>
+    <t>Alanine and Aspartate Metabolism</t>
+  </si>
+  <si>
+    <t>Beta-Alanine metabolism</t>
+  </si>
+  <si>
+    <t>E2367,E941</t>
+  </si>
+  <si>
+    <t>C00750,C06486/C00386</t>
+  </si>
+  <si>
+    <t>Spermine$(6R)-6-(L-erythro-1,2-Dihydroxypropyl)-5,6,7,8-tetrahydro-4a-/Carnosine; Nalpha-(beta-alanyl)-L-histidine</t>
+  </si>
+  <si>
+    <t>Glutathione Metabolism</t>
+  </si>
+  <si>
+    <t>E1575</t>
+  </si>
+  <si>
+    <t>Prostaglandin formation from arachidonate</t>
+  </si>
+  <si>
+    <t>E491,E1114,E1060,E785,E1115,E436,E935,E434</t>
+  </si>
+  <si>
+    <t>,,,,,C00020/C00362,,C00020/C00362</t>
+  </si>
+  <si>
+    <t>$$$$$AMP/dGMP$$AMP/dGMP</t>
+  </si>
+  <si>
+    <t>Vitamin B9 (folate) metabolism</t>
+  </si>
+  <si>
+    <t>E975,E371</t>
+  </si>
+  <si>
+    <t>Glycerophospholipid metabolism</t>
+  </si>
+  <si>
+    <t>E951,E2260,E2151,E222,E600,E955</t>
+  </si>
+  <si>
+    <t>,C00588/C05594,C06426/C06427,C00021,C04805/C04742/C14749/C14748/C14778/C14770/C14771/C14769/C14768/CE5016,</t>
+  </si>
+  <si>
+    <t>$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate$S-Adenosyl-L-homocysteine$5-Hydroxyeicosatetraenoate/(15S)-15-Hydroxy-5,8,11-cis-13-trans-eicosatetraenoate; (15S)-15-Hydroxy-5,8,11-cis-13-trans-icosatetraenoate; (5Z,8Z,11Z,13E)-(15S)-15-Hydroxyicosa-5,8,11,13-tetraenoic acid; 15(S)-HETE/19(S)-HETE; (19S)-Hydroxyeicosatetraenoic acid; (19S)-Hydroxyicosatetraenoic acid; (19S)-Hydroxy arachidonic acid/20-Hydroxyeicosatetraenoic acid/16(R)-HETE; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyeicosa-5,8,11,14-tetraenoic acid; (5Z,8Z,11Z,14Z)-(16R)-16-Hydroxyicosa-5,8,11,14-tetraenoic acid/11,12-EET/14,15-EET; (5Z,8Z,11Z)-14,15-Epoxyeicosa-5.8.11-trienoic acid; (5Z,8Z,11Z)-14,15-Epoxyicosa-5.8.11-trienoic acid/8,9-EET; (5Z,11Z,14Z)-8,9-Epoxyeicosa-5,11,14-trienoic acid; (5Z,11Z,14Z)-8,9-Epoxyicosa-5,11,14-trienoic acid/5,6-EET; (8Z,11Z,14Z)-5,6-Epoxyeicosa-8,11,14-trienoic acid; (8Z,11Z,14Z)-5,6-Epoxyicosa-8,11,14-trienoic acid/13,14-dihydroxy-retinol$</t>
+  </si>
+  <si>
+    <t>Leukotriene metabolism</t>
+  </si>
+  <si>
+    <t>E1948,E1008,E2686,E1060,E104,E2320,E436,E434,E1208,E734</t>
+  </si>
+  <si>
+    <t>,,,,,,C00020/C00362,C00020/C00362,,</t>
+  </si>
+  <si>
+    <t>$$$$$$AMP/dGMP$AMP/dGMP$$</t>
+  </si>
+  <si>
+    <t>Keratan sulfate degradation</t>
+  </si>
+  <si>
+    <t>E677</t>
+  </si>
+  <si>
+    <t>Starch and Sucrose Metabolism</t>
+  </si>
+  <si>
+    <t>E60</t>
+  </si>
+  <si>
+    <t>Sialic acid metabolism</t>
+  </si>
+  <si>
+    <t>E1818,E677,E60</t>
   </si>
   <si>
     <t>,,</t>
@@ -121,658 +667,160 @@
     <t>$$</t>
   </si>
   <si>
-    <t>Androgen and estrogen biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2119,E1899,E997,E919,E1409,E725,E784,E364,E995,E998,E1181,E1891,E238,E1908,E764,E785,E996,E1182</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,C00021,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$S-Adenosyl-L-homocysteine$$$$$</t>
-  </si>
-  <si>
-    <t>Glyoxylate and Dicarboxylate Metabolism</t>
-  </si>
-  <si>
-    <t>E189</t>
-  </si>
-  <si>
-    <t>Vitamin B12 (cyanocobalamin) metabolism</t>
-  </si>
-  <si>
-    <t>E238</t>
-  </si>
-  <si>
-    <t>C00021</t>
-  </si>
-  <si>
-    <t>S-Adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t>Vitamin A (retinol) metabolism</t>
-  </si>
-  <si>
-    <t>E70,E924,E616,E452,E923,E617,E1019</t>
-  </si>
-  <si>
-    <t>,,,C00020/C00362,,,</t>
-  </si>
-  <si>
-    <t>$$$AMP/dGMP$$$</t>
-  </si>
-  <si>
-    <t>Methionine and cysteine metabolism</t>
-  </si>
-  <si>
-    <t>E467,E640,E452,E238,E1032,E470,E468</t>
-  </si>
-  <si>
-    <t>C00170,,C00020/C00362,C00021,C01137,C00170,C00170</t>
-  </si>
-  <si>
-    <t>5-Methylthioadenosine$$AMP/dGMP$S-Adenosyl-L-homocysteine$S-Adenosylmethioninamine$5-Methylthioadenosine$5-Methylthioadenosine</t>
-  </si>
-  <si>
-    <t>Vitamin B3 (nicotinate and nicotinamide) metabolism</t>
-  </si>
-  <si>
-    <t>E910,E452,E238,E533</t>
-  </si>
-  <si>
-    <t>,C00020/C00362,C00021,</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP$S-Adenosyl-L-homocysteine$</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - ganglioseries</t>
-  </si>
-  <si>
-    <t>E340,E339,E2279</t>
-  </si>
-  <si>
-    <t>CoA Catabolism</t>
-  </si>
-  <si>
-    <t>E452,E2303,E560</t>
-  </si>
-  <si>
-    <t>C00020/C00362,,</t>
-  </si>
-  <si>
-    <t>AMP/dGMP$$</t>
-  </si>
-  <si>
-    <t>Alanine and Aspartate Metabolism</t>
-  </si>
-  <si>
-    <t>E1008,E1704,E452</t>
-  </si>
-  <si>
-    <t>C03406,,C00020/C00362</t>
-  </si>
-  <si>
-    <t>N-(L-Arginino)succinate; 2-(Nomega-L-Arginino)succinate; L-Argininosuccinate; L-Argininosuccinic acid; L-Arginosuccinic acid$$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Arachidonic acid metabolism</t>
-  </si>
-  <si>
-    <t>E17,E624,E1078,E1024,E616,E452,E1025,E617,E1077</t>
-  </si>
-  <si>
-    <t>,,,,,C00020/C00362,,,</t>
-  </si>
-  <si>
-    <t>$$$$$AMP/dGMP$$$</t>
-  </si>
-  <si>
-    <t>Pentose and Glucuronate Interconversions</t>
-  </si>
-  <si>
-    <t>E189,E187</t>
-  </si>
-  <si>
-    <t>,</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>Selenoamino acid metabolism</t>
-  </si>
-  <si>
-    <t>E640,E452</t>
-  </si>
-  <si>
-    <t>,C00020/C00362</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP</t>
-  </si>
-  <si>
-    <t>C21-steroid hormone biosynthesis and metabolism</t>
-  </si>
-  <si>
-    <t>E2119,E997,E998,E591,E1409,E784,E350,E1891,E785,E1899,E919,E2148,E1181,E635,E4,E764,E1182,E725,E995,E996</t>
-  </si>
-  <si>
-    <t>,,,,,,,,,,,,,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$$$$$$$$$$$$$</t>
-  </si>
-  <si>
-    <t>Glycerophospholipid metabolism</t>
-  </si>
-  <si>
-    <t>E972,E903,E1921,E616,E2268,E1152,E238,E20,E2260,E617</t>
-  </si>
-  <si>
-    <t>,C04874,,,C00588/C05594,,C00021,,,</t>
-  </si>
-  <si>
-    <t>$Dihydroneopterin$$$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$$S-Adenosyl-L-homocysteine$$$</t>
-  </si>
-  <si>
-    <t>Pyrimidine metabolism</t>
-  </si>
-  <si>
-    <t>E1320,E168,E452,E1205,E167,E2279</t>
-  </si>
-  <si>
-    <t>,,C00020/C00362,,,</t>
-  </si>
-  <si>
-    <t>$$AMP/dGMP$$$</t>
-  </si>
-  <si>
-    <t>Drug metabolism - cytochrome P450</t>
-  </si>
-  <si>
-    <t>E222,E225,E374,E436,E214,E1438,E223,E828,E209,E224,E226,E432,E143</t>
-  </si>
-  <si>
-    <t>,,,,C05635/C16596,C16586/CE2173,,,C05635/C16596,,,,</t>
-  </si>
-  <si>
-    <t>$$$$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$2-Phenyl-1,3-propanediol monocarbamate/$$$5-Hydroxyindoleacetate/5-Phenyl-1,3-oxazinane-2,4-dione$$$$</t>
+    <t>Galactose metabolism</t>
+  </si>
+  <si>
+    <t>Aminosugars metabolism</t>
+  </si>
+  <si>
+    <t>E677,E1629</t>
+  </si>
+  <si>
+    <t>Limonene and pinene degradation</t>
+  </si>
+  <si>
+    <t>E2152,E235</t>
+  </si>
+  <si>
+    <t>Purine metabolism</t>
+  </si>
+  <si>
+    <t>E830,E436,E628,E1569,E434,E624,E173</t>
+  </si>
+  <si>
+    <t>,C00020/C00362,,C00559/C05198,C00020/C00362,C00212/C00330,</t>
+  </si>
+  <si>
+    <t>$AMP/dGMP$$Deoxyadenosine/5'-Deoxyadenosine$AMP/dGMP$Adenosine/Deoxyguanosine$</t>
+  </si>
+  <si>
+    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
+  </si>
+  <si>
+    <t>E496</t>
+  </si>
+  <si>
+    <t>Linoleate metabolism</t>
+  </si>
+  <si>
+    <t>E143,E2418,E252,E251,E949,E1386,E1929,E2151</t>
+  </si>
+  <si>
+    <t>,,,,,,,C06426/C06427</t>
+  </si>
+  <si>
+    <t>$$$$$$$(6Z,9Z,12Z)-Octadecatrienoic acid; 6,9,12-Octadecatrienoic acid; gamma-Linolenic acid; Gamolenic acid/(9Z,12Z,15Z)-Octadecatrienoic acid; alpha-Linolenic acid; 9,12,15-Octadecatrienoic acid; Linolenate; alpha-Linolenate</t>
+  </si>
+  <si>
+    <t>Caffeine metabolism</t>
+  </si>
+  <si>
+    <t>E1225</t>
+  </si>
+  <si>
+    <t>CE5542/C16353</t>
+  </si>
+  <si>
+    <t>noradrenochrome o-semiquinone/</t>
+  </si>
+  <si>
+    <t>D4&amp;E4-neuroprostanes formation</t>
+  </si>
+  <si>
+    <t>E1881</t>
+  </si>
+  <si>
+    <t>Phosphatidylinositol phosphate metabolism</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid metabolism</t>
+  </si>
+  <si>
+    <t>E2260,E1304</t>
+  </si>
+  <si>
+    <t>C00588/C05594,</t>
+  </si>
+  <si>
+    <t>Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$</t>
+  </si>
+  <si>
+    <t>N-Glycan Degradation</t>
+  </si>
+  <si>
+    <t>Xenobiotics metabolism</t>
+  </si>
+  <si>
+    <t>E578</t>
+  </si>
+  <si>
+    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
+  </si>
+  <si>
+    <t>E1236,E171</t>
+  </si>
+  <si>
+    <t>Fructose and mannose metabolism</t>
+  </si>
+  <si>
+    <t>E1676</t>
+  </si>
+  <si>
+    <t>N-Glycan biosynthesis</t>
+  </si>
+  <si>
+    <t>R Group Synthesis</t>
   </si>
   <si>
     <t>C5-Branched dibasic acid metabolism</t>
   </si>
   <si>
-    <t>E2279</t>
-  </si>
-  <si>
-    <t>Chondroitin sulfate degradation</t>
-  </si>
-  <si>
-    <t>Mono-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>E452</t>
-  </si>
-  <si>
-    <t>C00020/C00362</t>
-  </si>
-  <si>
-    <t>AMP/dGMP</t>
-  </si>
-  <si>
-    <t>Phytanic acid peroxisomal oxidation</t>
-  </si>
-  <si>
-    <t>Bile acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E775,E452,E1954,E1641,E1955,E2273,E1479</t>
-  </si>
-  <si>
-    <t>,C00020/C00362,,,,,</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP$$$$$</t>
-  </si>
-  <si>
-    <t>Limonene and pinene degradation</t>
-  </si>
-  <si>
-    <t>E250,E253,E251,E2164</t>
-  </si>
-  <si>
-    <t>,,,</t>
-  </si>
-  <si>
-    <t>$$$</t>
-  </si>
-  <si>
-    <t>Pentose phosphate pathway</t>
-  </si>
-  <si>
-    <t>E1202,E452,E189,E187</t>
-  </si>
-  <si>
-    <t>,C00020/C00362,,</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP$$</t>
-  </si>
-  <si>
-    <t>Lysine metabolism</t>
-  </si>
-  <si>
-    <t>E650,E298,E452,E238</t>
-  </si>
-  <si>
-    <t>,,C00020/C00362,C00021</t>
-  </si>
-  <si>
-    <t>$$AMP/dGMP$S-Adenosyl-L-homocysteine</t>
-  </si>
-  <si>
-    <t>Prostaglandin formation from arachidonate</t>
-  </si>
-  <si>
-    <t>E17,E952,E1792,E1078,E801,E452,E1131,E1914,E1077,E507</t>
-  </si>
-  <si>
-    <t>,,C02670/C00072/glac,,,C00020/C00362,,,,</t>
-  </si>
-  <si>
-    <t>$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$AMP/dGMP$$$$</t>
-  </si>
-  <si>
-    <t>Hexose phosphorylation</t>
-  </si>
-  <si>
-    <t>E76,E1003,E1098,E1004,E1090,E1093</t>
-  </si>
-  <si>
-    <t>,,C05838/C00811/C02763/C00166,,C05838/C00811/C02763/C00166,C05838/C00811/C02763/C00166</t>
-  </si>
-  <si>
-    <t>$$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate</t>
-  </si>
-  <si>
-    <t>Porphyrin metabolism</t>
-  </si>
-  <si>
-    <t>E152,E378,E1792,E150</t>
-  </si>
-  <si>
-    <t>,,C02670/C00072/glac,</t>
-  </si>
-  <si>
-    <t>$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
+    <t>Pyruvate Metabolism</t>
+  </si>
+  <si>
+    <t>Squalene and cholesterol biosynthesis</t>
+  </si>
+  <si>
+    <t>Glycerolipid metabolism</t>
+  </si>
+  <si>
+    <t>Carnitine shuttle</t>
+  </si>
+  <si>
+    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
+  </si>
+  <si>
+    <t>Glycosphingolipid biosynthesis - globoseries</t>
+  </si>
+  <si>
+    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
   </si>
   <si>
     <t>Glycosphingolipid biosynthesis - lactoseries</t>
   </si>
   <si>
+    <t>Parathio degradation</t>
+  </si>
+  <si>
     <t>Blood Group Biosynthesis</t>
   </si>
   <si>
+    <t>Heparan sulfate biosynthesis</t>
+  </si>
+  <si>
+    <t>Fatty Acid Metabolism</t>
+  </si>
+  <si>
+    <t>Glycosaminoglycan degradation</t>
+  </si>
+  <si>
+    <t>ROS Detoxification</t>
+  </si>
+  <si>
+    <t>Saturated fatty acids beta-oxidation</t>
+  </si>
+  <si>
     <t>Glycosphingolipid biosynthesis - neolactoseries</t>
-  </si>
-  <si>
-    <t>Glutathione Metabolism</t>
-  </si>
-  <si>
-    <t>E1590</t>
-  </si>
-  <si>
-    <t>Omega-6 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>Hyaluronan Metabolism</t>
-  </si>
-  <si>
-    <t>E568,E693</t>
-  </si>
-  <si>
-    <t>Vitamin B1 (thiamin) metabolism</t>
-  </si>
-  <si>
-    <t>E298,E452</t>
-  </si>
-  <si>
-    <t>Vitamin E metabolism</t>
-  </si>
-  <si>
-    <t>E976,E452</t>
-  </si>
-  <si>
-    <t>Heparan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E189,E693</t>
-  </si>
-  <si>
-    <t>Fatty acid activation</t>
-  </si>
-  <si>
-    <t>E1668,E452</t>
-  </si>
-  <si>
-    <t>Vitamin B5 - CoA biosynthesis from pantothenate</t>
-  </si>
-  <si>
-    <t>Leukotriene metabolism</t>
-  </si>
-  <si>
-    <t>E17,E1225,E1961,E1078,E127,E1024,E1223,E452,E120,E1025,E750,E1077,E1963</t>
-  </si>
-  <si>
-    <t>,,,,,,,C00020/C00362,,,,,</t>
-  </si>
-  <si>
-    <t>$$$$$$$AMP/dGMP$$$$$</t>
-  </si>
-  <si>
-    <t>Histidine metabolism</t>
-  </si>
-  <si>
-    <t>E95,E452,E238,E953</t>
-  </si>
-  <si>
-    <t>Vitamin B6 (pyridoxine) metabolism</t>
-  </si>
-  <si>
-    <t>E332,E318,E688,E2094</t>
-  </si>
-  <si>
-    <t>,C00547/C00314,,</t>
-  </si>
-  <si>
-    <t>$Norepinephrine/Pyridoxine$$</t>
-  </si>
-  <si>
-    <t>Ubiquinone Biosynthesis</t>
-  </si>
-  <si>
-    <t>E452,E238,E1098,E1090,E1093</t>
-  </si>
-  <si>
-    <t>C00020/C00362,C00021,C05838/C00811/C02763/C00166,C05838/C00811/C02763/C00166,C05838/C00811/C02763/C00166</t>
-  </si>
-  <si>
-    <t>AMP/dGMP$S-Adenosyl-L-homocysteine$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate$cis-2-Hydroxycinnamate; 2-Coumarinate/4-Coumarate; p-Coumaric acid; trans-4-Hydroxycinnamate; trans-p-Hydroxycinnamate; 4-Hydroxycinnamic acid; 4-Hydroxycinnamate/enol-Phenylpyruvate/Phenylpyruvate</t>
-  </si>
-  <si>
-    <t>Glycine, serine, alanine and threonine metabolism</t>
-  </si>
-  <si>
-    <t>E815,E452,E238,E1751,E814,E1255</t>
-  </si>
-  <si>
-    <t>,C00020/C00362,C00021,,,</t>
-  </si>
-  <si>
-    <t>$AMP/dGMP$S-Adenosyl-L-homocysteine$$$</t>
-  </si>
-  <si>
-    <t>Vitamin B2 (riboflavin) metabolism</t>
-  </si>
-  <si>
-    <t>E452,E843</t>
-  </si>
-  <si>
-    <t>C00020/C00362,</t>
-  </si>
-  <si>
-    <t>AMP/dGMP$</t>
-  </si>
-  <si>
-    <t>Di-unsaturated fatty acid beta-oxidation</t>
-  </si>
-  <si>
-    <t>Valine, leucine and isoleucine degradation</t>
-  </si>
-  <si>
-    <t>Sialic acid metabolism</t>
-  </si>
-  <si>
-    <t>E76,E1833,E1152,E693</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid metabolism</t>
-  </si>
-  <si>
-    <t>E10,E20,E2268,E2279</t>
-  </si>
-  <si>
-    <t>,,C00588/C05594,</t>
-  </si>
-  <si>
-    <t>$$Choline phosphate/3-Methoxy-4-hydroxyphenylethyleneglycol$</t>
-  </si>
-  <si>
-    <t>Putative anti-Inflammatory metabolites formation from EPA</t>
-  </si>
-  <si>
-    <t>E513,E517</t>
-  </si>
-  <si>
-    <t>Squalene and cholesterol biosynthesis</t>
-  </si>
-  <si>
-    <t>E2113,E1808</t>
-  </si>
-  <si>
-    <t>De novo fatty acid biosynthesis</t>
-  </si>
-  <si>
-    <t>E70,E452</t>
-  </si>
-  <si>
-    <t>Fructose and mannose metabolism</t>
-  </si>
-  <si>
-    <t>E1691,E1690,E2204,E2279</t>
-  </si>
-  <si>
-    <t>Propanoate metabolism</t>
-  </si>
-  <si>
-    <t>Vitamin H (biotin) metabolism</t>
-  </si>
-  <si>
-    <t>Omega-3 fatty acid metabolism</t>
-  </si>
-  <si>
-    <t>Linoleate metabolism</t>
-  </si>
-  <si>
-    <t>E1400,E267,E1943,E1792,E1401,E268,E484,E487,E2109,E966,E159</t>
-  </si>
-  <si>
-    <t>,,,C02670/C00072/glac,,,,,,,</t>
-  </si>
-  <si>
-    <t>$$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$$$$$</t>
-  </si>
-  <si>
-    <t>D4&amp;E4-neuroprostanes formation</t>
-  </si>
-  <si>
-    <t>E1792,E1896</t>
-  </si>
-  <si>
-    <t>C02670/C00072/glac,</t>
-  </si>
-  <si>
-    <t>D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol phosphate metabolism</t>
-  </si>
-  <si>
-    <t>E76,E1152</t>
-  </si>
-  <si>
-    <t>Purine metabolism</t>
-  </si>
-  <si>
-    <t>E1855,E644,E1792,E1796,E640,E452,E189,E846,E2279</t>
-  </si>
-  <si>
-    <t>C00147,,C02670/C00072/glac,,,C00020/C00362,,,</t>
-  </si>
-  <si>
-    <t>Adenine$$D-glucurono-6,3-lactone/L-Ascorbate/D-glucurono-6,3-lactone$$$AMP/dGMP$$$</t>
-  </si>
-  <si>
-    <t>Aspartate and asparagine metabolism</t>
-  </si>
-  <si>
-    <t>E452,E1146,E1720,E1590</t>
-  </si>
-  <si>
-    <t>C00020/C00362,C00437,,</t>
-  </si>
-  <si>
-    <t>AMP/dGMP$N2-Acetyl-L-ornithine$$</t>
-  </si>
-  <si>
-    <t>Keratan sulfate degradation</t>
-  </si>
-  <si>
-    <t>E693</t>
-  </si>
-  <si>
-    <t>Lipoate metabolism</t>
-  </si>
-  <si>
-    <t>E1655</t>
-  </si>
-  <si>
-    <t>Starch and Sucrose Metabolism</t>
-  </si>
-  <si>
-    <t>E76</t>
-  </si>
-  <si>
-    <t>Glycolysis and Gluconeogenesis</t>
-  </si>
-  <si>
-    <t>E452,E2279</t>
-  </si>
-  <si>
-    <t>Vitamin B9 (folate) metabolism</t>
-  </si>
-  <si>
-    <t>E1704,E992</t>
-  </si>
-  <si>
-    <t>Butanoate metabolism</t>
-  </si>
-  <si>
-    <t>E452,E311</t>
-  </si>
-  <si>
-    <t>Ascorbate (Vitamin C) and Aldarate Metabolism</t>
-  </si>
-  <si>
-    <t>E1197,E1253,E1792,E187</t>
-  </si>
-  <si>
-    <t>Vitamin D3 (cholecalciferol) metabolism</t>
-  </si>
-  <si>
-    <t>E8</t>
-  </si>
-  <si>
-    <t>Glycosphingolipid biosynthesis - globoseries</t>
-  </si>
-  <si>
-    <t>Beta-Alanine metabolism</t>
-  </si>
-  <si>
-    <t>E953</t>
-  </si>
-  <si>
-    <t>Galactose metabolism</t>
-  </si>
-  <si>
-    <t>E76,E1833,E693</t>
-  </si>
-  <si>
-    <t>Xenobiotics metabolism</t>
-  </si>
-  <si>
-    <t>E1631,E594</t>
-  </si>
-  <si>
-    <t>Caffeine metabolism</t>
-  </si>
-  <si>
-    <t>E1242</t>
-  </si>
-  <si>
-    <t>CE5542/C16353</t>
-  </si>
-  <si>
-    <t>noradrenochrome o-semiquinone/</t>
-  </si>
-  <si>
-    <t>Carnitine shuttle</t>
-  </si>
-  <si>
-    <t>E1338,E1341,E1330,E1340</t>
-  </si>
-  <si>
-    <t>TCA cycle</t>
-  </si>
-  <si>
-    <t>N-Glycan biosynthesis</t>
-  </si>
-  <si>
-    <t>N-Glycan Degradation</t>
-  </si>
-  <si>
-    <t>Aminosugars metabolism</t>
-  </si>
-  <si>
-    <t>R Group Synthesis</t>
-  </si>
-  <si>
-    <t>Pyruvate Metabolism</t>
-  </si>
-  <si>
-    <t>Glycerolipid metabolism</t>
-  </si>
-  <si>
-    <t>3-oxo-10R-octadecatrienoate beta-oxidation</t>
-  </si>
-  <si>
-    <t>Glycosylphosphatidylinositol(GPI)-anchor biosynthesis</t>
-  </si>
-  <si>
-    <t>Parathio degradation</t>
-  </si>
-  <si>
-    <t>Electron transport chain</t>
-  </si>
-  <si>
-    <t>Heparan sulfate biosynthesis</t>
-  </si>
-  <si>
-    <t>Fatty Acid Metabolism</t>
-  </si>
-  <si>
-    <t>Glycosaminoglycan degradation</t>
-  </si>
-  <si>
-    <t>Fatty acid oxidation</t>
-  </si>
-  <si>
-    <t>ROS Detoxification</t>
-  </si>
-  <si>
-    <t>Saturated fatty acids beta-oxidation</t>
   </si>
   <si>
     <t>Geraniol degradation</t>
@@ -1198,13 +1246,13 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>0.0147046466683472</v>
+        <v>0.001193257256180568</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1221,13 +1269,13 @@
         <v>11</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C3">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>0.01831778842114108</v>
+        <v>0.002117611468714811</v>
       </c>
       <c r="E3" t="s">
         <v>12</v>
@@ -1244,13 +1292,13 @@
         <v>15</v>
       </c>
       <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
         <v>5</v>
       </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
       <c r="D4">
-        <v>0.01899000084026552</v>
+        <v>0.007445253020957631</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1267,13 +1315,13 @@
         <v>19</v>
       </c>
       <c r="B5">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D5">
-        <v>0.01974623981178052</v>
+        <v>0.010436799381523</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
@@ -1290,13 +1338,13 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>0.02293924880262163</v>
+        <v>0.01089057326767617</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
@@ -1313,13 +1361,13 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="C7">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>0.03932442651877993</v>
+        <v>0.01198299188248937</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
@@ -1336,13 +1384,13 @@
         <v>31</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D8">
-        <v>0.08486681791446098</v>
+        <v>0.01218466916522411</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -1359,13 +1407,13 @@
         <v>35</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C9">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>0.09276531383917318</v>
+        <v>0.01877279373455908</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -1382,372 +1430,390 @@
         <v>39</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D10">
-        <v>0.1078060667170826</v>
+        <v>0.02063830859985546</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
       </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="D11">
-        <v>0.1078060667170826</v>
+        <v>0.02171392077444077</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B12">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C12">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0.1123435005461726</v>
+        <v>0.02265508142720291</v>
       </c>
       <c r="E12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>0.02265508142720291</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" t="s">
         <v>49</v>
       </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>19</v>
-      </c>
-      <c r="D13">
-        <v>0.1123435005461726</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>50</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>19</v>
+      </c>
+      <c r="D14">
+        <v>0.02783146501739467</v>
+      </c>
+      <c r="E14" t="s">
         <v>53</v>
       </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14">
-        <v>10</v>
-      </c>
-      <c r="D14">
-        <v>0.1263759347953954</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>54</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>55</v>
-      </c>
-      <c r="G14" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>19</v>
+      </c>
+      <c r="D15">
+        <v>0.02783146501739467</v>
+      </c>
+      <c r="E15" t="s">
         <v>57</v>
       </c>
-      <c r="B15">
-        <v>3</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-      <c r="D15">
-        <v>0.1318376607007815</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>58</v>
       </c>
-      <c r="F15" t="s">
-        <v>33</v>
-      </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>0.1318376607007815</v>
+        <v>0.04035226298717669</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>0.1318376607007815</v>
+        <v>0.04596561402329372</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>0.1320057138055626</v>
+        <v>0.05201593250533604</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19">
         <v>2</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>0.1320057138055626</v>
+        <v>0.05415035041427875</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B20">
         <v>2</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20">
-        <v>0.1320057138055626</v>
+        <v>0.05415035041427875</v>
       </c>
       <c r="E20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C21">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>0.1478867322073775</v>
+        <v>0.05415035041427875</v>
       </c>
       <c r="E21" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C22">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>0.150071422569532</v>
+        <v>0.05878892791717786</v>
       </c>
       <c r="E22" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B23">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="D23">
-        <v>0.1526762456936392</v>
+        <v>0.07524243290028738</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B24">
+        <v>5</v>
+      </c>
+      <c r="C24">
         <v>13</v>
       </c>
-      <c r="C24">
-        <v>41</v>
-      </c>
       <c r="D24">
-        <v>0.1783043441727586</v>
+        <v>0.07542730374279424</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D25">
-        <v>0.219057222082178</v>
+        <v>0.08120871918119023</v>
       </c>
       <c r="E25" t="s">
-        <v>96</v>
+        <v>91</v>
+      </c>
+      <c r="F25" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>7</v>
+      </c>
+      <c r="D26">
+        <v>0.08798171459303206</v>
+      </c>
+      <c r="E26" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" t="s">
         <v>97</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26">
-        <v>0.219057222082178</v>
-      </c>
-      <c r="E26" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1755,13 +1821,13 @@
         <v>98</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>0.219057222082178</v>
+        <v>0.08798171459303206</v>
       </c>
       <c r="E27" t="s">
         <v>99</v>
@@ -1778,1347 +1844,1311 @@
         <v>102</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D28">
-        <v>0.219057222082178</v>
+        <v>0.08798171459303206</v>
       </c>
       <c r="E28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C29">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>0.2361986387698513</v>
+        <v>0.09053629350767214</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
-      </c>
-      <c r="F29" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>0.2583816486009579</v>
+        <v>0.09053629350767214</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31">
-        <v>0.2583816486009579</v>
+        <v>0.09828406245273189</v>
       </c>
       <c r="E31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32">
         <v>4</v>
       </c>
-      <c r="C32">
-        <v>13</v>
-      </c>
       <c r="D32">
-        <v>0.2583816486009579</v>
+        <v>0.09937648106754508</v>
       </c>
       <c r="E32" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="F32" t="s">
-        <v>117</v>
+        <v>49</v>
       </c>
       <c r="G32" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>0.2768674901268801</v>
+        <v>0.09937648106754508</v>
       </c>
       <c r="E33" t="s">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="F33" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B34">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>0.2834215612133434</v>
+        <v>0.09937648106754508</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G34" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B35">
         <v>4</v>
       </c>
       <c r="C35">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>0.2911520040332745</v>
+        <v>0.118653468008941</v>
       </c>
       <c r="E35" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F35" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G35" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D36">
-        <v>0.3069489958826989</v>
+        <v>0.118653468008941</v>
       </c>
       <c r="E36" t="s">
-        <v>96</v>
+        <v>127</v>
+      </c>
+      <c r="F36" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
+        <v>130</v>
+      </c>
+      <c r="B37">
+        <v>12</v>
+      </c>
+      <c r="C37">
+        <v>41</v>
+      </c>
+      <c r="D37">
+        <v>0.1380649064721601</v>
+      </c>
+      <c r="E37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F37" t="s">
         <v>132</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37">
-        <v>0.3069489958826989</v>
-      </c>
-      <c r="E37" t="s">
-        <v>96</v>
+      <c r="G37" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D38">
-        <v>0.3069489958826989</v>
+        <v>0.1424345809314129</v>
       </c>
       <c r="E38" t="s">
-        <v>96</v>
+        <v>135</v>
+      </c>
+      <c r="F38" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D39">
-        <v>0.3069489958826989</v>
+        <v>0.1480815448479857</v>
       </c>
       <c r="E39" t="s">
-        <v>135</v>
+        <v>139</v>
+      </c>
+      <c r="F39" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D40">
-        <v>0.3069489958826989</v>
+        <v>0.1480815448479857</v>
       </c>
       <c r="E40" t="s">
-        <v>99</v>
+        <v>143</v>
       </c>
       <c r="F40" t="s">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="B41">
         <v>2</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D41">
-        <v>0.3117385093689606</v>
+        <v>0.1548377338195997</v>
       </c>
       <c r="E41" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="G41" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="B42">
         <v>2</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D42">
-        <v>0.3117385093689606</v>
+        <v>0.1548377338195997</v>
       </c>
       <c r="E42" t="s">
-        <v>140</v>
+        <v>48</v>
       </c>
       <c r="F42" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="G42" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B43">
+        <v>1</v>
+      </c>
+      <c r="C43">
         <v>2</v>
       </c>
-      <c r="C43">
-        <v>7</v>
-      </c>
       <c r="D43">
-        <v>0.3117385093689606</v>
+        <v>0.1826523923967664</v>
       </c>
       <c r="E43" t="s">
-        <v>142</v>
-      </c>
-      <c r="F43" t="s">
-        <v>77</v>
-      </c>
-      <c r="G43" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D44">
-        <v>0.3117385093689606</v>
+        <v>0.1843666493000118</v>
       </c>
       <c r="E44" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F44" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="G44" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="B45">
         <v>2</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45">
-        <v>0.3117385093689606</v>
+        <v>0.1997949614292197</v>
       </c>
       <c r="E45" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F45" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="G45" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D46">
-        <v>0.3216536425510461</v>
+        <v>0.1997949614292197</v>
       </c>
       <c r="E46" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="F46" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="G46" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B47">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C47">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D47">
-        <v>0.3340895723048483</v>
+        <v>0.2008873800440329</v>
       </c>
       <c r="E47" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="F47" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="G47" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D48">
-        <v>0.3341735988572389</v>
+        <v>0.2141812742642981</v>
       </c>
       <c r="E48" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>165</v>
       </c>
       <c r="G48" t="s">
-        <v>56</v>
+        <v>166</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="D49">
-        <v>0.3341735988572389</v>
+        <v>0.2341809381354935</v>
       </c>
       <c r="E49" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F49" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="G49" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D50">
-        <v>0.3488782455255861</v>
+        <v>0.2415757718357675</v>
       </c>
       <c r="E50" t="s">
-        <v>159</v>
+        <v>99</v>
       </c>
       <c r="F50" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D51">
-        <v>0.3658516091084783</v>
+        <v>0.2415757718357675</v>
       </c>
       <c r="E51" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F51" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="G51" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D52">
-        <v>0.3920678934543316</v>
+        <v>0.2415757718357675</v>
       </c>
       <c r="E52" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F52" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G52" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>0.411646080161331</v>
+        <v>0.2470546713500613</v>
       </c>
       <c r="E53" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="F53" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G53" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D54">
-        <v>0.411646080161331</v>
+        <v>0.2470546713500613</v>
       </c>
       <c r="E54" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="F54" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G54" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D55">
-        <v>0.4324006386017982</v>
+        <v>0.2470546713500613</v>
       </c>
       <c r="E55" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F55" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G55" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D56">
-        <v>0.4324006386017982</v>
+        <v>0.2470546713500613</v>
       </c>
       <c r="E56" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="F56" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="G56" t="s">
-        <v>177</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D57">
-        <v>0.442819931098227</v>
+        <v>0.2470546713500613</v>
       </c>
       <c r="E57" t="s">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="F57" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="G57" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>0.442819931098227</v>
+        <v>0.2470546713500613</v>
       </c>
       <c r="E58" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F58" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="G58" t="s">
-        <v>74</v>
+        <v>192</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D59">
-        <v>0.442819931098227</v>
+        <v>0.263172047528613</v>
       </c>
       <c r="E59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F59" t="s">
-        <v>77</v>
-      </c>
-      <c r="G59" t="s">
-        <v>78</v>
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C60">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D60">
-        <v>0.4691202419964709</v>
+        <v>0.3574561772071058</v>
       </c>
       <c r="E60" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F60" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="G60" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D61">
-        <v>0.4729854634064364</v>
+        <v>0.4357909951093259</v>
       </c>
       <c r="E61" t="s">
-        <v>99</v>
+        <v>200</v>
       </c>
       <c r="F61" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="G61" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D62">
-        <v>0.4729854634064364</v>
+        <v>0.4361439303541117</v>
       </c>
       <c r="E62" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="F62" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="G62" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="D63">
-        <v>0.4729854634064364</v>
+        <v>0.4380598645400918</v>
       </c>
       <c r="E63" t="s">
-        <v>99</v>
+        <v>206</v>
       </c>
       <c r="F63" t="s">
-        <v>100</v>
+        <v>207</v>
       </c>
       <c r="G63" t="s">
-        <v>101</v>
+        <v>208</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B64">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D64">
-        <v>0.4784471893118226</v>
+        <v>0.4486815347641216</v>
       </c>
       <c r="E64" t="s">
-        <v>190</v>
-      </c>
-      <c r="F64" t="s">
-        <v>191</v>
-      </c>
-      <c r="G64" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D65">
-        <v>0.4828165700361314</v>
+        <v>0.4486815347641216</v>
       </c>
       <c r="E65" t="s">
-        <v>194</v>
-      </c>
-      <c r="F65" t="s">
-        <v>195</v>
-      </c>
-      <c r="G65" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D66">
-        <v>0.4828165700361314</v>
+        <v>0.4644627821381153</v>
       </c>
       <c r="E66" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="F66" t="s">
-        <v>73</v>
+        <v>215</v>
       </c>
       <c r="G66" t="s">
-        <v>74</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B67">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="D67">
-        <v>0.4895386942273758</v>
+        <v>0.4644627821381153</v>
       </c>
       <c r="E67" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="F67" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G67" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C68">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D68">
-        <v>0.4924796235610453</v>
+        <v>0.4679921345859733</v>
       </c>
       <c r="E68" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F68" t="s">
-        <v>205</v>
+        <v>120</v>
       </c>
       <c r="G68" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D69">
-        <v>0.5165952440971346</v>
+        <v>0.5005462093074066</v>
       </c>
       <c r="E69" t="s">
-        <v>208</v>
+        <v>221</v>
+      </c>
+      <c r="F69" t="s">
+        <v>120</v>
+      </c>
+      <c r="G69" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D70">
-        <v>0.5165952440971346</v>
+        <v>0.5298230281844003</v>
       </c>
       <c r="E70" t="s">
-        <v>210</v>
+        <v>223</v>
+      </c>
+      <c r="F70" t="s">
+        <v>224</v>
+      </c>
+      <c r="G70" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D71">
-        <v>0.5165952440971346</v>
+        <v>0.5580410413270365</v>
       </c>
       <c r="E71" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C72">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D72">
-        <v>0.5179396689353836</v>
+        <v>0.5585284280936454</v>
       </c>
       <c r="E72" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="F72" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="G72" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D73">
-        <v>0.5179396689353836</v>
+        <v>0.573704643619435</v>
       </c>
       <c r="E73" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="F73" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="G73" t="s">
-        <v>74</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D74">
-        <v>0.5179396689353836</v>
+        <v>0.573704643619435</v>
       </c>
       <c r="E74" t="s">
-        <v>218</v>
-      </c>
-      <c r="F74" t="s">
-        <v>168</v>
-      </c>
-      <c r="G74" t="s">
-        <v>169</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D75">
-        <v>0.5432316612049407</v>
+        <v>0.573704643619435</v>
       </c>
       <c r="E75" t="s">
-        <v>220</v>
-      </c>
-      <c r="F75" t="s">
-        <v>129</v>
-      </c>
-      <c r="G75" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D76">
-        <v>0.552642635072683</v>
+        <v>0.5811498966403926</v>
       </c>
       <c r="E76" t="s">
-        <v>222</v>
+        <v>240</v>
+      </c>
+      <c r="F76" t="s">
+        <v>241</v>
+      </c>
+      <c r="G76" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D77">
-        <v>0.552642635072683</v>
+        <v>0.6024940757298196</v>
       </c>
       <c r="E77" t="s">
-        <v>96</v>
+        <v>210</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D78">
-        <v>0.552642635072683</v>
+        <v>0.6142921967698022</v>
       </c>
       <c r="E78" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D79">
-        <v>0.5544912192252752</v>
+        <v>0.6220063528344062</v>
       </c>
       <c r="E79" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="F79" t="s">
-        <v>33</v>
+        <v>120</v>
       </c>
       <c r="G79" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>18</v>
+      </c>
+      <c r="D80">
+        <v>0.6368632459958656</v>
+      </c>
+      <c r="E80" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>12</v>
+      </c>
+      <c r="D81">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>251</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>252</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
         <v>2</v>
       </c>
-      <c r="C80">
-        <v>13</v>
-      </c>
-      <c r="D80">
-        <v>0.577010335265944</v>
-      </c>
-      <c r="E80" t="s">
-        <v>229</v>
-      </c>
-      <c r="F80" t="s">
-        <v>73</v>
-      </c>
-      <c r="G80" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" t="s">
-        <v>230</v>
-      </c>
-      <c r="B81">
+      <c r="D83">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>253</v>
+      </c>
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
         <v>1</v>
       </c>
-      <c r="C81">
-        <v>10</v>
-      </c>
-      <c r="D81">
-        <v>0.6253256028905134</v>
-      </c>
-      <c r="E81" t="s">
-        <v>231</v>
-      </c>
-      <c r="F81" t="s">
-        <v>232</v>
-      </c>
-      <c r="G81" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" t="s">
-        <v>234</v>
-      </c>
-      <c r="B82">
-        <v>4</v>
-      </c>
-      <c r="C82">
+      <c r="D84">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>254</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>9</v>
+      </c>
+      <c r="D85">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>255</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>256</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
         <v>26</v>
       </c>
-      <c r="D82">
-        <v>0.6262498949668095</v>
-      </c>
-      <c r="E82" t="s">
-        <v>235</v>
-      </c>
-      <c r="F82" t="s">
-        <v>109</v>
-      </c>
-      <c r="G82" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" t="s">
-        <v>236</v>
-      </c>
-      <c r="B83">
-        <v>1</v>
-      </c>
-      <c r="C83">
+      <c r="D87">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>257</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
         <v>11</v>
       </c>
-      <c r="D83">
-        <v>0.6370052936728006</v>
-      </c>
-      <c r="E83" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7">
-      <c r="A84" t="s">
-        <v>237</v>
-      </c>
-      <c r="B84">
-        <v>1</v>
-      </c>
-      <c r="C84">
-        <v>12</v>
-      </c>
-      <c r="D84">
-        <v>0.6471725065120578</v>
-      </c>
-      <c r="E84" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" t="s">
-        <v>238</v>
-      </c>
-      <c r="B85">
-        <v>1</v>
-      </c>
-      <c r="C85">
-        <v>12</v>
-      </c>
-      <c r="D85">
-        <v>0.6471725065120578</v>
-      </c>
-      <c r="E85" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" t="s">
-        <v>239</v>
-      </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="C86">
-        <v>12</v>
-      </c>
-      <c r="D86">
-        <v>0.6471725065120578</v>
-      </c>
-      <c r="E86" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87" t="s">
-        <v>240</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88" t="s">
-        <v>241</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
-      </c>
-      <c r="C88">
-        <v>1</v>
-      </c>
       <c r="D88">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="B89">
         <v>0</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D89">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="B90">
         <v>0</v>
       </c>
       <c r="C90">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="B91">
         <v>0</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D91">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -3127,12 +3157,12 @@
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -3141,12 +3171,12 @@
         <v>3</v>
       </c>
       <c r="D93">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -3155,12 +3185,12 @@
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -3169,12 +3199,12 @@
         <v>4</v>
       </c>
       <c r="D95">
-        <v>0.6764977732963616</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>0.6448799179845717</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -3183,54 +3213,54 @@
         <v>0</v>
       </c>
       <c r="D96">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="B97">
         <v>0</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="B98">
         <v>0</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B99">
         <v>0</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D99">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -3239,12 +3269,12 @@
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -3253,12 +3283,12 @@
         <v>0</v>
       </c>
       <c r="D101">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -3267,12 +3297,12 @@
         <v>0</v>
       </c>
       <c r="D102">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -3281,12 +3311,12 @@
         <v>0</v>
       </c>
       <c r="D103">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -3295,12 +3325,12 @@
         <v>0</v>
       </c>
       <c r="D104">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -3309,12 +3339,12 @@
         <v>1</v>
       </c>
       <c r="D105">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -3323,12 +3353,12 @@
         <v>0</v>
       </c>
       <c r="D106">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -3337,12 +3367,12 @@
         <v>0</v>
       </c>
       <c r="D107">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -3351,12 +3381,12 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -3365,12 +3395,12 @@
         <v>0</v>
       </c>
       <c r="D109">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -3379,12 +3409,12 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -3393,12 +3423,12 @@
         <v>2</v>
       </c>
       <c r="D111">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -3407,12 +3437,12 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -3421,12 +3451,12 @@
         <v>0</v>
       </c>
       <c r="D113">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -3435,12 +3465,12 @@
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -3449,12 +3479,12 @@
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -3463,12 +3493,12 @@
         <v>0</v>
       </c>
       <c r="D116">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -3477,12 +3507,12 @@
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -3491,12 +3521,12 @@
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -3505,12 +3535,12 @@
         <v>3</v>
       </c>
       <c r="D119">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -3519,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0.6764977732963616</v>
+        <v>0.6448799179845717</v>
       </c>
     </row>
   </sheetData>
